--- a/data/trans_dic/P44D-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P44D-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,29</t>
+          <t>0,0; 9,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,75</t>
+          <t>0,0; 10,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,14</t>
+          <t>1,1; 6,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 19,99</t>
+          <t>3,17; 19,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,3</t>
+          <t>0,0; 10,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,55</t>
+          <t>0,23; 2,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 13,11</t>
+          <t>2,5; 12,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,71</t>
+          <t>0,0; 6,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,56</t>
+          <t>0,91; 3,47</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,62; 33,27</t>
+          <t>7,01; 33,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 23,57</t>
+          <t>6,66; 23,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 9,0</t>
+          <t>5,7; 11,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,24; 48,56</t>
+          <t>10,35; 46,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 24,39</t>
+          <t>3,18; 26,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 9,59</t>
+          <t>4,64; 9,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,52; 33,11</t>
+          <t>11,04; 33,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 20,22</t>
+          <t>7,31; 20,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 8,03</t>
+          <t>5,9; 9,87</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,69; 68,93</t>
+          <t>7,12; 66,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,0; 61,94</t>
+          <t>22,9; 63,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,85; 27,8</t>
+          <t>14,72; 27,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,48; 76,31</t>
+          <t>16,34; 75,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,33; 70,2</t>
+          <t>17,13; 69,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,11; 28,03</t>
+          <t>14,96; 28,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,83; 60,71</t>
+          <t>19,98; 59,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,06; 56,38</t>
+          <t>25,92; 56,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,49; 25,95</t>
+          <t>16,69; 26,15</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 22,96</t>
+          <t>6,58; 22,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 21,07</t>
+          <t>9,58; 20,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 10,55</t>
+          <t>7,47; 12,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,85; 28,07</t>
+          <t>10,85; 27,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 17,83</t>
+          <t>5,09; 17,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 9,18</t>
+          <t>5,78; 9,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,48; 22,32</t>
+          <t>10,14; 21,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,15; 17,34</t>
+          <t>9,19; 18,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 9,03</t>
+          <t>7,29; 10,18</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6378</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5950</t>
+          <t>0; 4833</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5681</t>
+          <t>0; 5609</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1521; 8704</t>
+          <t>1657; 9473</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2084; 12987</t>
+          <t>2058; 12621</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6108</t>
+          <t>0; 6416</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>408; 4360</t>
+          <t>433; 4389</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2946; 14871</t>
+          <t>2831; 13957</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 7524</t>
+          <t>0; 7207</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2979; 11112</t>
+          <t>3101; 11771</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>24388</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>16694</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>37214</t>
+          <t>41082</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3224; 16200</t>
+          <t>3415; 16511</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4981; 17642</t>
+          <t>4981; 17245</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5430; 46037</t>
+          <t>16578; 34353</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3116; 14782</t>
+          <t>3150; 14301</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1017; 7793</t>
+          <t>1015; 8559</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10294; 21398</t>
+          <t>11355; 23267</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9113; 26203</t>
+          <t>8738; 26488</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7472; 21600</t>
+          <t>7812; 22316</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13528; 59003</t>
+          <t>31581; 52861</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25605</t>
+          <t>27490</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18294</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43899</t>
+          <t>47419</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1510; 10744</t>
+          <t>1109; 10428</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6367; 17926</t>
+          <t>6628; 18252</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18399; 34451</t>
+          <t>19153; 36282</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2308; 9530</t>
+          <t>2041; 9466</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2960; 11333</t>
+          <t>2766; 11203</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12950; 24026</t>
+          <t>14532; 27192</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6129; 17045</t>
+          <t>5610; 16826</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11299; 25421</t>
+          <t>11687; 25430</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34576; 54404</t>
+          <t>37919; 59411</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51933</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35281</t>
+          <t>38506</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>87214</t>
+          <t>94879</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7959; 25874</t>
+          <t>7418; 25094</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14860; 32994</t>
+          <t>15008; 32444</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22006; 82021</t>
+          <t>42751; 70709</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11709; 30289</t>
+          <t>11704; 29349</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5470; 19144</t>
+          <t>5468; 18775</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27459; 44017</t>
+          <t>30610; 49095</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23128; 49239</t>
+          <t>22359; 46921</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24158; 45783</t>
+          <t>24250; 47618</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44711; 113486</t>
+          <t>80323; 112123</t>
         </is>
       </c>
     </row>
